--- a/세모이 자판 설명/세모이 자판 약어 (가나다순).xlsx
+++ b/세모이 자판 설명/세모이 자판 약어 (가나다순).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f585cdba73fdfdd1/바탕 화면/세모이 230116/dist/세모이 자판 설명/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="11_E7C820F66345650C63036355446BE708D4802C44" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCDC51F8-ADEF-471C-95A3-BE995393687F}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="11_E7C820F66345650C63036355446BE708D4802C44" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5CD9CA8-EBF8-4205-8B67-744CFEEBED57}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="29010" windowHeight="15945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="15840" windowWidth="29010" windowHeight="15945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -7550,7 +7550,7 @@
         <v>1719</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>5</v>
       </c>
@@ -7585,7 +7585,7 @@
         <v>1719</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>6</v>
       </c>
@@ -14773,7 +14773,7 @@
       <c r="D456" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="F456" s="2" t="s">
+      <c r="E456" s="2" t="s">
         <v>400</v>
       </c>
     </row>
@@ -25980,7 +25980,7 @@
       <c r="D1174" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="E1174" s="2" t="s">
+      <c r="F1174" s="2" t="s">
         <v>498</v>
       </c>
     </row>
@@ -28782,7 +28782,7 @@
       <c r="D1354" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="E1354" s="2" t="s">
+      <c r="F1354" s="2" t="s">
         <v>498</v>
       </c>
     </row>

--- a/세모이 자판 설명/세모이 자판 약어 (가나다순).xlsx
+++ b/세모이 자판 설명/세모이 자판 약어 (가나다순).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f585cdba73fdfdd1/바탕 화면/세모이 230116/dist/세모이 자판 설명/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\Git\semoe\세모이 자판 설명\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="11_E7C820F66345650C63036355446BE708D4802C44" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5CD9CA8-EBF8-4205-8B67-744CFEEBED57}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD85880F-0C8C-41FB-89ED-E88ABC2DF1C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28695" yWindow="15840" windowWidth="29010" windowHeight="15945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28860,6 +28860,9 @@
       </c>
     </row>
     <row r="1360" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1360" s="3">
+        <v>1351</v>
+      </c>
       <c r="B1360" s="2" t="s">
         <v>330</v>
       </c>
@@ -28870,7 +28873,10 @@
         <v>56</v>
       </c>
     </row>
-    <row r="1361" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="1361" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1361" s="3">
+        <v>1352</v>
+      </c>
       <c r="B1361" s="2" t="s">
         <v>1109</v>
       </c>
@@ -28884,7 +28890,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1362" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="1362" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1362" s="3">
+        <v>1353</v>
+      </c>
       <c r="B1362" s="2" t="s">
         <v>803</v>
       </c>
@@ -28895,7 +28904,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1363" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="1363" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1363" s="3">
+        <v>1354</v>
+      </c>
       <c r="B1363" s="2" t="s">
         <v>635</v>
       </c>
@@ -28906,7 +28918,10 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1364" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="1364" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1364" s="3">
+        <v>1355</v>
+      </c>
       <c r="B1364" s="2" t="s">
         <v>1413</v>
       </c>
@@ -28921,7 +28936,10 @@
       </c>
       <c r="L1364" s="3"/>
     </row>
-    <row r="1365" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="1365" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1365" s="3">
+        <v>1356</v>
+      </c>
       <c r="B1365" s="2" t="s">
         <v>804</v>
       </c>
@@ -28933,7 +28951,10 @@
       </c>
       <c r="L1365" s="3"/>
     </row>
-    <row r="1366" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="1366" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1366" s="3">
+        <v>1357</v>
+      </c>
       <c r="B1366" s="2" t="s">
         <v>1174</v>
       </c>
@@ -28948,7 +28969,10 @@
       </c>
       <c r="L1366" s="3"/>
     </row>
-    <row r="1367" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="1367" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1367" s="3">
+        <v>1358</v>
+      </c>
       <c r="B1367" s="2" t="s">
         <v>1502</v>
       </c>
@@ -28966,7 +28990,10 @@
       </c>
       <c r="L1367" s="3"/>
     </row>
-    <row r="1368" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="1368" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1368" s="3">
+        <v>1359</v>
+      </c>
       <c r="B1368" s="2" t="s">
         <v>537</v>
       </c>
@@ -28978,28 +29005,28 @@
       </c>
       <c r="L1368" s="3"/>
     </row>
-    <row r="1369" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="1369" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L1369" s="3"/>
     </row>
-    <row r="1370" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="1370" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L1370" s="3"/>
     </row>
-    <row r="1371" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="1371" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L1371" s="3"/>
     </row>
-    <row r="1372" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="1372" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L1372" s="3"/>
     </row>
-    <row r="1373" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="1373" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L1373" s="3"/>
     </row>
-    <row r="1374" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="1374" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L1374" s="3"/>
     </row>
-    <row r="1375" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="1375" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L1375" s="3"/>
     </row>
-    <row r="1376" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="1376" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L1376" s="3"/>
     </row>
   </sheetData>
